--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.21900545261944</v>
+        <v>6.04808838605066</v>
       </c>
       <c r="D2" t="n">
-        <v>37.04293297022332</v>
+        <v>6.019476607661289</v>
       </c>
       <c r="E2" t="n">
-        <v>13.26966064934063</v>
+        <v>2.156319855517852</v>
       </c>
       <c r="F2" t="n">
-        <v>13.15358516879009</v>
+        <v>2.13745758992839</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.2337936007527</v>
+        <v>2.312991460122314</v>
       </c>
       <c r="D3" t="n">
-        <v>14.12971708552999</v>
+        <v>2.296079026398623</v>
       </c>
       <c r="E3" t="n">
-        <v>13.26966064934063</v>
+        <v>2.156319855517852</v>
       </c>
       <c r="F3" t="n">
-        <v>13.15358516879009</v>
+        <v>2.13745758992839</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.21696608415238</v>
+        <v>4.260256988674763</v>
       </c>
       <c r="D4" t="n">
-        <v>26.22809953308546</v>
+        <v>4.262066174126388</v>
       </c>
       <c r="E4" t="n">
-        <v>13.26966064934063</v>
+        <v>2.156319855517852</v>
       </c>
       <c r="F4" t="n">
-        <v>13.15358516879009</v>
+        <v>2.13745758992839</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.56816025741671</v>
+        <v>4.317326041830215</v>
       </c>
       <c r="D5" t="n">
-        <v>26.67066895083662</v>
+        <v>4.333983704510951</v>
       </c>
       <c r="E5" t="n">
-        <v>13.26966064934063</v>
+        <v>2.156319855517852</v>
       </c>
       <c r="F5" t="n">
-        <v>13.15358516879009</v>
+        <v>2.13745758992839</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.80281487526272</v>
+        <v>8.742957417230192</v>
       </c>
       <c r="D6" t="n">
-        <v>53.4435150148899</v>
+        <v>8.684571189919609</v>
       </c>
       <c r="E6" t="n">
-        <v>13.26966064934063</v>
+        <v>2.156319855517852</v>
       </c>
       <c r="F6" t="n">
-        <v>13.15358516879009</v>
+        <v>2.13745758992839</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
